--- a/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/abr-2026.xlsx
+++ b/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/abr-2026.xlsx
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>4351423.02</v>
+        <v>4846.3</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>18275503.54</v>
+        <v>20353.92</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>10886100.96</v>
+        <v>12124.14</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>3155880</v>
+        <v>3514.79</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>3772185.76</v>
+        <v>4201.18</v>
       </c>
     </row>
   </sheetData>
